--- a/uploads/TPH HARMONY.xlsx
+++ b/uploads/TPH HARMONY.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="325">
   <si>
     <t>Sonia Sharma, Rajat Kant Sharma</t>
   </si>
@@ -997,6 +997,18 @@
   </si>
   <si>
     <t>RENT OUT</t>
+  </si>
+  <si>
+    <t>not ans</t>
+  </si>
+  <si>
+    <t>call cut</t>
+  </si>
+  <si>
+    <t>wrong no</t>
+  </si>
+  <si>
+    <t>NOT INT</t>
   </si>
 </sst>
 </file>
@@ -1685,6 +1697,9 @@
       <c r="C24" s="1" t="s">
         <v>65</v>
       </c>
+      <c r="D24" t="s" s="0">
+        <v>308</v>
+      </c>
     </row>
     <row r="25" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -1696,6 +1711,9 @@
       <c r="C25" s="1" t="s">
         <v>68</v>
       </c>
+      <c r="D25" t="s" s="0">
+        <v>308</v>
+      </c>
     </row>
     <row r="26" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
@@ -1707,6 +1725,9 @@
       <c r="C26" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="D26" t="s" s="0">
+        <v>311</v>
+      </c>
     </row>
     <row r="27" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
@@ -1718,6 +1739,9 @@
       <c r="C27" s="1" t="s">
         <v>74</v>
       </c>
+      <c r="D27" t="s" s="0">
+        <v>311</v>
+      </c>
     </row>
     <row r="28" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
@@ -1738,6 +1762,9 @@
       <c r="C29" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="D29" t="s" s="0">
+        <v>308</v>
+      </c>
     </row>
     <row r="30" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
@@ -1749,6 +1776,9 @@
       <c r="C30" s="1" t="s">
         <v>81</v>
       </c>
+      <c r="D30" t="s" s="0">
+        <v>324</v>
+      </c>
     </row>
     <row r="31" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
@@ -1760,6 +1790,9 @@
       <c r="C31" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="D31" t="s" s="0">
+        <v>324</v>
+      </c>
     </row>
     <row r="32" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
@@ -2304,6 +2337,9 @@
       <c r="C81" s="1" t="s">
         <v>226</v>
       </c>
+      <c r="D81" t="s" s="0">
+        <v>308</v>
+      </c>
     </row>
     <row r="82" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
@@ -2315,6 +2351,9 @@
       <c r="C82" s="1" t="s">
         <v>39</v>
       </c>
+      <c r="D82" t="s" s="0">
+        <v>308</v>
+      </c>
     </row>
     <row r="83" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
@@ -2335,6 +2374,9 @@
       <c r="C84" s="1" t="s">
         <v>232</v>
       </c>
+      <c r="D84" t="s" s="0">
+        <v>318</v>
+      </c>
     </row>
     <row r="85" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
@@ -2355,6 +2397,9 @@
       <c r="C86" s="1" t="s">
         <v>236</v>
       </c>
+      <c r="D86" t="s" s="0">
+        <v>321</v>
+      </c>
     </row>
     <row r="87" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
@@ -2366,6 +2411,9 @@
       <c r="C87" s="1" t="s">
         <v>239</v>
       </c>
+      <c r="D87" t="s" s="0">
+        <v>323</v>
+      </c>
     </row>
     <row r="88" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
@@ -2377,6 +2425,9 @@
       <c r="C88" s="1" t="s">
         <v>242</v>
       </c>
+      <c r="D88" t="s" s="0">
+        <v>322</v>
+      </c>
     </row>
     <row r="89" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
@@ -2387,6 +2438,9 @@
       </c>
       <c r="C89" s="1" t="s">
         <v>245</v>
+      </c>
+      <c r="D89" t="s" s="0">
+        <v>321</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="18.75" x14ac:dyDescent="0.3">
